--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.05107990217998</v>
+        <v>11.54580048410425</v>
       </c>
       <c r="D2" t="n">
-        <v>98.73304613769817</v>
+        <v>16.04411999737595</v>
       </c>
       <c r="E2" t="n">
-        <v>16.12250697019331</v>
+        <v>2.619907382656414</v>
       </c>
       <c r="F2" t="n">
-        <v>18.52826201034525</v>
+        <v>3.010842576681104</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.49388624052055</v>
+        <v>9.667756514084591</v>
       </c>
       <c r="D3" t="n">
-        <v>86.86091254047078</v>
+        <v>14.1148982878265</v>
       </c>
       <c r="E3" t="n">
-        <v>16.12250697019331</v>
+        <v>2.619907382656414</v>
       </c>
       <c r="F3" t="n">
-        <v>18.52826201034525</v>
+        <v>3.010842576681104</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.81006556029197</v>
+        <v>7.931635653547446</v>
       </c>
       <c r="D4" t="n">
-        <v>68.41379440891919</v>
+        <v>11.11724159144937</v>
       </c>
       <c r="E4" t="n">
-        <v>16.12250697019331</v>
+        <v>2.619907382656414</v>
       </c>
       <c r="F4" t="n">
-        <v>18.52826201034525</v>
+        <v>3.010842576681104</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.5632947122922</v>
+        <v>3.179035390747484</v>
       </c>
       <c r="D5" t="n">
-        <v>42.43849199221241</v>
+        <v>6.896254948734517</v>
       </c>
       <c r="E5" t="n">
-        <v>16.12250697019331</v>
+        <v>2.619907382656414</v>
       </c>
       <c r="F5" t="n">
-        <v>18.52826201034525</v>
+        <v>3.010842576681104</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.66123518345611</v>
+        <v>4.982450717311618</v>
       </c>
       <c r="D6" t="n">
-        <v>48.28643137476233</v>
+        <v>7.846545098398879</v>
       </c>
       <c r="E6" t="n">
-        <v>16.12250697019331</v>
+        <v>2.619907382656414</v>
       </c>
       <c r="F6" t="n">
-        <v>18.52826201034525</v>
+        <v>3.010842576681104</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.42505553884775</v>
+        <v>8.844071525062759</v>
       </c>
       <c r="D7" t="n">
-        <v>69.4347479289079</v>
+        <v>11.28314653844753</v>
       </c>
       <c r="E7" t="n">
-        <v>16.12250697019331</v>
+        <v>2.619907382656414</v>
       </c>
       <c r="F7" t="n">
-        <v>18.52826201034525</v>
+        <v>3.010842576681104</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>50.29783792570014</v>
+        <v>8.173398662926274</v>
       </c>
       <c r="D8" t="n">
-        <v>60.32532464918842</v>
+        <v>9.802865255493119</v>
       </c>
       <c r="E8" t="n">
-        <v>16.12250697019331</v>
+        <v>2.619907382656414</v>
       </c>
       <c r="F8" t="n">
-        <v>18.52826201034525</v>
+        <v>3.010842576681104</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
